--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run6/epoch_140/per_file_predictions_epoch_140.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run6/epoch_140/per_file_predictions_epoch_140.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="486">
   <si>
     <t>Filename</t>
   </si>
@@ -808,685 +808,670 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9938,0.0005,0.0012,0.0001</t>
-  </si>
-  <si>
-    <t>0.0016,0.0001,0.0000,0.9995</t>
-  </si>
-  <si>
-    <t>0.9889,0.0016,0.0008,0.0029</t>
-  </si>
-  <si>
-    <t>0.0765,0.0003,0.0001,0.9792</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>0.9846,0.0029,0.0033,0.0005</t>
+  </si>
+  <si>
+    <t>0.0084,0.0000,0.0000,0.9983</t>
+  </si>
+  <si>
+    <t>0.9818,0.0004,0.0000,0.0073</t>
+  </si>
+  <si>
+    <t>0.0557,0.0016,0.0004,0.9750</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0001,0.0001</t>
   </si>
   <si>
     <t>1.0000,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9851,0.0003,0.0126,0.0000</t>
-  </si>
-  <si>
-    <t>0.2371,0.0010,0.8056,0.0001</t>
-  </si>
-  <si>
-    <t>0.0404,0.0019,0.9661,0.0001</t>
-  </si>
-  <si>
-    <t>0.0009,0.0001,0.9989,0.0001</t>
-  </si>
-  <si>
-    <t>0.8350,0.0002,0.2361,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0008,0.0000</t>
+    <t>0.9954,0.0061,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0094,0.0009,0.9843,0.0005</t>
+  </si>
+  <si>
+    <t>0.0092,0.0032,0.9870,0.0001</t>
+  </si>
+  <si>
+    <t>0.2614,0.0060,0.7246,0.0001</t>
+  </si>
+  <si>
+    <t>0.0042,0.0005,0.9949,0.0001</t>
+  </si>
+  <si>
+    <t>0.9860,0.0001,0.0196,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0291,0.9786,0.0012,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.9980,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9704,0.0005,0.0148,0.0005</t>
+  </si>
+  <si>
+    <t>0.0016,0.0040,0.9939,0.0054</t>
+  </si>
+  <si>
+    <t>0.0018,0.0003,0.9972,0.0006</t>
+  </si>
+  <si>
+    <t>0.1585,0.0007,0.8365,0.0005</t>
+  </si>
+  <si>
+    <t>0.0159,0.0000,0.9882,0.0001</t>
+  </si>
+  <si>
+    <t>0.8340,0.0001,0.2295,0.0001</t>
+  </si>
+  <si>
+    <t>0.0014,0.0004,0.9960,0.0021</t>
+  </si>
+  <si>
+    <t>0.0083,0.9933,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.3284,0.6122,0.0087,0.0013</t>
+  </si>
+  <si>
+    <t>0.0001,0.0016,0.9994,0.0072</t>
+  </si>
+  <si>
+    <t>0.0024,0.9971,0.0008,0.0003</t>
+  </si>
+  <si>
+    <t>0.9550,0.0004,0.0411,0.0006</t>
+  </si>
+  <si>
+    <t>0.9092,0.0000,0.1524,0.0002</t>
+  </si>
+  <si>
+    <t>0.4852,0.5714,0.0019,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.9992,0.0029,0.0001</t>
+  </si>
+  <si>
+    <t>0.0182,0.9303,0.0198,0.0008</t>
+  </si>
+  <si>
+    <t>0.0196,0.0002,0.9649,0.0012</t>
+  </si>
+  <si>
+    <t>0.0145,0.0124,0.9639,0.0010</t>
+  </si>
+  <si>
+    <t>0.0980,0.0001,0.8586,0.0028</t>
+  </si>
+  <si>
+    <t>0.0004,0.0089,0.9979,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0010,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0166,0.0419,0.0024,0.9723</t>
+  </si>
+  <si>
+    <t>0.0012,0.9990,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0057,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0027,0.9992,0.0001</t>
+  </si>
+  <si>
+    <t>0.0013,0.0024,0.9966,0.0001</t>
+  </si>
+  <si>
+    <t>0.0167,0.0001,0.9776,0.0017</t>
+  </si>
+  <si>
+    <t>0.0004,0.0002,0.9991,0.0006</t>
+  </si>
+  <si>
+    <t>0.0006,0.0006,0.9979,0.0005</t>
+  </si>
+  <si>
+    <t>0.0002,0.0065,0.9981,0.0013</t>
+  </si>
+  <si>
+    <t>0.9939,0.0069,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0039,0.9996,0.0048</t>
+  </si>
+  <si>
+    <t>0.9993,0.0004,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9969,0.9984,0.0000</t>
+  </si>
+  <si>
+    <t>0.0014,0.0019,0.9948,0.0016</t>
+  </si>
+  <si>
+    <t>0.0005,0.0001,0.9981,0.0009</t>
+  </si>
+  <si>
+    <t>0.0000,0.9975,0.9973,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.0043,0.9971,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.8764,0.0002,0.2547,0.0000</t>
+  </si>
+  <si>
+    <t>0.8440,0.0054,0.1110,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.0002,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0009,0.9323,0.6383,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.1843,0.9963,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9963,0.9564,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.0005,0.9996</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0023,0.0000,0.0000,0.9997</t>
+  </si>
+  <si>
+    <t>0.0042,0.0002,0.0003,0.9980</t>
+  </si>
+  <si>
+    <t>0.0005,0.0000,0.0000,0.9998</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9977,0.2628,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.9933,0.9982,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9853,0.8512,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.6033,0.9285,0.0019</t>
+  </si>
+  <si>
+    <t>0.0000,0.9917,0.9740,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9937,0.7958,0.0001</t>
+  </si>
+  <si>
+    <t>0.9999,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0014,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9984,0.0011,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9997,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0005,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9989,0.0010,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0026</t>
+  </si>
+  <si>
+    <t>0.0020,0.0024,0.9959,0.0002</t>
+  </si>
+  <si>
+    <t>0.1149,0.0003,0.8579,0.0067</t>
+  </si>
+  <si>
+    <t>0.0018,0.0003,0.9979,0.0002</t>
   </si>
   <si>
     <t>0.0001,0.9999,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.0142,0.9915,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0001,0.0000</t>
-  </si>
-  <si>
     <t>0.0000,1.0000,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.8203,0.0027,0.1409,0.0007</t>
-  </si>
-  <si>
-    <t>0.0513,0.0005,0.9148,0.0043</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9997,0.0008</t>
-  </si>
-  <si>
-    <t>0.0085,0.0008,0.9794,0.0026</t>
-  </si>
-  <si>
-    <t>0.0045,0.0001,0.9958,0.0000</t>
-  </si>
-  <si>
-    <t>0.4921,0.0004,0.5963,0.0003</t>
-  </si>
-  <si>
-    <t>0.0003,0.0003,0.9985,0.0026</t>
-  </si>
-  <si>
-    <t>0.3236,0.7730,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.2588,0.5304,0.0503,0.0005</t>
-  </si>
-  <si>
-    <t>0.0001,0.0012,0.9998,0.0041</t>
-  </si>
-  <si>
-    <t>0.0002,0.9998,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9952,0.0006,0.0031,0.0002</t>
-  </si>
-  <si>
-    <t>0.9981,0.0004,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0542,0.9570,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.0010,0.9974,0.0122,0.0001</t>
-  </si>
-  <si>
-    <t>0.0130,0.9421,0.0309,0.0007</t>
-  </si>
-  <si>
-    <t>0.0029,0.0004,0.9892,0.0027</t>
-  </si>
-  <si>
-    <t>0.0166,0.0059,0.9662,0.0014</t>
-  </si>
-  <si>
-    <t>0.0036,0.0002,0.9897,0.0060</t>
-  </si>
-  <si>
-    <t>0.0001,0.0222,0.9986,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.0059,0.9985,0.0024</t>
-  </si>
-  <si>
-    <t>0.0212,0.1018,0.0036,0.9283</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0030,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.2565,0.9976,0.0002</t>
-  </si>
-  <si>
-    <t>0.0004,0.0036,0.9986,0.0001</t>
-  </si>
-  <si>
-    <t>0.0045,0.0000,0.9955,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9998,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0008,0.9996,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.0314,0.9977,0.0009</t>
-  </si>
-  <si>
-    <t>0.9947,0.0058,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9955,0.0004,0.0044,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.9984,0.0350</t>
+    <t>0.0020,0.9972,0.0015,0.0000</t>
+  </si>
+  <si>
+    <t>0.0034,0.9946,0.0050,0.0000</t>
+  </si>
+  <si>
+    <t>0.1443,0.8785,0.0020,0.0000</t>
+  </si>
+  <si>
+    <t>0.3945,0.0043,0.3864,0.0064</t>
+  </si>
+  <si>
+    <t>0.0566,0.0002,0.9452,0.0004</t>
+  </si>
+  <si>
+    <t>0.8279,0.0243,0.0498,0.0010</t>
+  </si>
+  <si>
+    <t>0.8608,0.0192,0.0265,0.0026</t>
+  </si>
+  <si>
+    <t>0.0004,0.0391,0.0010,0.9955</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9986,0.9812,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0015,0.0000</t>
+  </si>
+  <si>
+    <t>0.9820,0.0194,0.0013,0.0000</t>
+  </si>
+  <si>
+    <t>0.7529,0.2411,0.0033,0.0003</t>
+  </si>
+  <si>
+    <t>0.9984,0.0007,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.7473,0.9860,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.7890,0.9977,0.0000</t>
+  </si>
+  <si>
+    <t>0.0045,0.0029,0.9888,0.0003</t>
+  </si>
+  <si>
+    <t>0.0031,0.0016,0.9945,0.0001</t>
+  </si>
+  <si>
+    <t>0.9967,0.0001,0.0009,0.0000</t>
+  </si>
+  <si>
+    <t>0.9894,0.0003,0.0047,0.0001</t>
+  </si>
+  <si>
+    <t>0.0059,0.0001,0.9940,0.0002</t>
+  </si>
+  <si>
+    <t>0.0223,0.0000,0.9820,0.0001</t>
+  </si>
+  <si>
+    <t>0.0490,0.0003,0.0002,0.9831</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0014,0.0000,0.0003,0.9990</t>
+  </si>
+  <si>
+    <t>0.0000,0.9987,0.6064,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.9988,0.0003,0.0003</t>
   </si>
   <si>
     <t>0.9999,0.0000,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.9996,0.0003,0.0000,0.0000</t>
+    <t>0.0995,0.9228,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.9989,0.0001,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.9899,0.0000,0.0004,0.0065</t>
+  </si>
+  <si>
+    <t>0.0004,0.0016,0.9981,0.0052</t>
+  </si>
+  <si>
+    <t>0.9948,0.0000,0.0071,0.0001</t>
+  </si>
+  <si>
+    <t>0.6361,0.4587,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9973,0.0012,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9966,0.0014,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.1515,0.0213,0.6544,0.0001</t>
+  </si>
+  <si>
+    <t>0.9974,0.0013,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9945,0.0031,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9983,0.0009,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.9994,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9857,0.0091,0.0000,0.0004</t>
+  </si>
+  <si>
+    <t>0.2929,0.6510,0.0093,0.0007</t>
+  </si>
+  <si>
+    <t>0.9512,0.0672,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0298,0.1108,0.9128,0.0004</t>
+  </si>
+  <si>
+    <t>0.9959,0.0017,0.0011,0.0010</t>
+  </si>
+  <si>
+    <t>0.9892,0.0134,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0007,1.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9915,0.0035,0.0030,0.0018</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0167,0.9977,0.0027</t>
+  </si>
+  <si>
+    <t>0.0006,0.0002,0.9991,0.0003</t>
+  </si>
+  <si>
+    <t>0.0008,0.0044,0.9973,0.0005</t>
+  </si>
+  <si>
+    <t>0.0002,0.0004,0.9995,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0002,0.9992,0.0003</t>
+  </si>
+  <si>
+    <t>0.0015,0.0012,0.9957,0.0009</t>
+  </si>
+  <si>
+    <t>0.0202,0.0001,0.9860,0.0001</t>
+  </si>
+  <si>
+    <t>0.2363,0.0110,0.6665,0.0003</t>
+  </si>
+  <si>
+    <t>0.0753,0.1320,0.5948,0.0003</t>
+  </si>
+  <si>
+    <t>0.0022,0.0356,0.9904,0.0001</t>
+  </si>
+  <si>
+    <t>0.7910,0.0010,0.2292,0.0001</t>
+  </si>
+  <si>
+    <t>0.9672,0.0006,0.0205,0.0002</t>
+  </si>
+  <si>
+    <t>0.0089,0.0007,0.9886,0.0013</t>
+  </si>
+  <si>
+    <t>0.0023,0.9981,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0070,0.9953,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0023,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0288,0.9771,0.0015,0.0000</t>
+  </si>
+  <si>
+    <t>0.0149,0.9896,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.5749,0.2377,0.0117,0.0015</t>
+  </si>
+  <si>
+    <t>0.9979,0.0000,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.9781,0.0003,0.0067,0.0008</t>
+  </si>
+  <si>
+    <t>0.4449,0.0042,0.3953,0.0018</t>
+  </si>
+  <si>
+    <t>0.9414,0.0018,0.0272,0.0020</t>
+  </si>
+  <si>
+    <t>0.0007,0.0002,0.9980,0.0025</t>
+  </si>
+  <si>
+    <t>0.0021,0.0320,0.9846,0.0028</t>
+  </si>
+  <si>
+    <t>0.0063,0.0366,0.9793,0.0007</t>
+  </si>
+  <si>
+    <t>0.0165,0.0012,0.9793,0.0003</t>
+  </si>
+  <si>
+    <t>0.0034,0.0828,0.8914,0.0081</t>
+  </si>
+  <si>
+    <t>0.9978,0.0016,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9952,0.0043,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9983,0.0012,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9954,0.0034,0.0007,0.0004</t>
+  </si>
+  <si>
+    <t>0.9968,0.0036,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0006</t>
+  </si>
+  <si>
+    <t>0.9716,0.0114,0.0083,0.0009</t>
+  </si>
+  <si>
+    <t>0.9960,0.0005,0.0014,0.0004</t>
+  </si>
+  <si>
+    <t>0.0024,0.0001,0.9975,0.0000</t>
+  </si>
+  <si>
+    <t>0.0093,0.0005,0.9888,0.0002</t>
+  </si>
+  <si>
+    <t>0.0015,0.0604,0.9887,0.0015</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0496,0.0007,0.9448,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.0002,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.0001,0.9982,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.0015,0.9974,0.0008</t>
+  </si>
+  <si>
+    <t>0.5135,0.0005,0.4740,0.0010</t>
+  </si>
+  <si>
+    <t>0.9649,0.0001,0.0366,0.0001</t>
+  </si>
+  <si>
+    <t>0.9857,0.0003,0.0029,0.0006</t>
+  </si>
+  <si>
+    <t>0.9992,0.0005,0.0001,0.0000</t>
   </si>
   <si>
     <t>0.9998,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0000,0.9527,0.9992,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0047,0.9993,0.0006</t>
-  </si>
-  <si>
-    <t>0.0007,0.0003,0.9976,0.0007</t>
-  </si>
-  <si>
-    <t>0.0000,0.9993,0.9954,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0009,0.9987,0.0015,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.1016,0.0004,0.9360,0.0002</t>
-  </si>
-  <si>
-    <t>0.9229,0.0067,0.0426,0.0003</t>
-  </si>
-  <si>
-    <t>0.0050,0.0005,0.9960,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.9868,0.3836,0.0004</t>
-  </si>
-  <si>
-    <t>0.0001,0.5218,0.9950,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.9974,0.0041,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9982,0.2276,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.0001,0.9998</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0013,0.0002,0.0010,0.9986</t>
-  </si>
-  <si>
-    <t>0.0013,0.0000,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9984,0.0190,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.9934,0.9983,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9920,0.9428,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0934,0.9986,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9794,0.9965,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9947,0.9686,0.0000</t>
-  </si>
-  <si>
-    <t>0.9986,0.0022,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9983,0.0014,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0005,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9988,0.0009,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9949,0.0059,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9998,0.0047</t>
-  </si>
-  <si>
-    <t>0.0033,0.0031,0.9931,0.0002</t>
-  </si>
-  <si>
-    <t>0.5190,0.0001,0.4164,0.0031</t>
-  </si>
-  <si>
-    <t>0.0075,0.0006,0.9913,0.0004</t>
-  </si>
-  <si>
-    <t>0.0005,0.9997,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0051,0.9922,0.0030,0.0001</t>
-  </si>
-  <si>
-    <t>0.0013,0.9975,0.0022,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9998,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.6767,0.4891,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.8619,0.0014,0.1123,0.0010</t>
-  </si>
-  <si>
-    <t>0.4128,0.0003,0.6141,0.0004</t>
-  </si>
-  <si>
-    <t>0.3182,0.4669,0.0120,0.0056</t>
-  </si>
-  <si>
-    <t>0.8996,0.0081,0.0430,0.0010</t>
-  </si>
-  <si>
-    <t>0.0018,0.0093,0.0005,0.9976</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0044,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0000,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,0.9990,0.9905,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9997,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.7194,0.2472,0.0083,0.0000</t>
-  </si>
-  <si>
-    <t>0.9111,0.0993,0.0022,0.0002</t>
-  </si>
-  <si>
-    <t>0.9986,0.0008,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0005,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0003,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9987,0.0001,0.0009,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.3165,0.9979,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.2120,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0015,0.0038,0.9946,0.0002</t>
-  </si>
-  <si>
-    <t>0.0006,0.0061,0.9982,0.0000</t>
-  </si>
-  <si>
-    <t>0.9619,0.0003,0.0248,0.0004</t>
-  </si>
-  <si>
-    <t>0.9901,0.0001,0.0079,0.0001</t>
-  </si>
-  <si>
-    <t>0.0945,0.0001,0.9150,0.0006</t>
-  </si>
-  <si>
-    <t>0.8746,0.0006,0.1047,0.0005</t>
-  </si>
-  <si>
-    <t>0.0567,0.0001,0.0004,0.9798</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.0001,0.9998</t>
-  </si>
-  <si>
-    <t>0.0000,0.9978,0.9232,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0024,0.9939,0.0026,0.0006</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.1344,0.8681,0.0023,0.0005</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.7157,0.0000,0.0172,0.1514</t>
-  </si>
-  <si>
-    <t>0.0008,0.0028,0.9970,0.0039</t>
-  </si>
-  <si>
-    <t>0.9461,0.0000,0.0363,0.0018</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0214,0.9840,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.9973,0.0007,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9914,0.0023,0.0035,0.0000</t>
-  </si>
-  <si>
-    <t>0.0151,0.9814,0.0036,0.0001</t>
-  </si>
-  <si>
-    <t>0.9752,0.0024,0.0156,0.0000</t>
-  </si>
-  <si>
-    <t>0.9968,0.0011,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9991,0.0002,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9977,0.0005,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.8988,0.1197,0.0013,0.0001</t>
-  </si>
-  <si>
-    <t>0.8783,0.1850,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.0024,0.1523,0.9886,0.0005</t>
-  </si>
-  <si>
-    <t>0.9990,0.0015,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9935,0.0026,0.0018,0.0026</t>
-  </si>
-  <si>
-    <t>0.9725,0.0448,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0010,1.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9755,0.0253,0.0024,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0235,0.9977,0.0008</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9997,0.0002</t>
-  </si>
-  <si>
-    <t>0.0037,0.0080,0.9895,0.0006</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9998,0.0005</t>
-  </si>
-  <si>
-    <t>0.0020,0.0015,0.9943,0.0007</t>
-  </si>
-  <si>
-    <t>0.1001,0.0019,0.8837,0.0007</t>
-  </si>
-  <si>
-    <t>0.1314,0.0097,0.8021,0.0003</t>
-  </si>
-  <si>
-    <t>0.1054,0.0557,0.7104,0.0001</t>
-  </si>
-  <si>
-    <t>0.0259,0.1053,0.8002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0359,0.0008,0.9677,0.0000</t>
-  </si>
-  <si>
-    <t>0.3311,0.0004,0.6458,0.0012</t>
-  </si>
-  <si>
-    <t>0.0296,0.0017,0.9609,0.0009</t>
-  </si>
-  <si>
-    <t>0.0108,0.9921,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0245,0.9843,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9583,0.0878,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9483,0.0969,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0971,0.9143,0.0035,0.0001</t>
-  </si>
-  <si>
-    <t>0.8482,0.0200,0.0417,0.0013</t>
-  </si>
-  <si>
-    <t>0.9974,0.0001,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.9511,0.0015,0.0170,0.0016</t>
-  </si>
-  <si>
-    <t>0.8137,0.0069,0.1324,0.0004</t>
-  </si>
-  <si>
-    <t>0.6852,0.0317,0.0762,0.0110</t>
-  </si>
-  <si>
-    <t>0.0019,0.0001,0.9974,0.0005</t>
-  </si>
-  <si>
-    <t>0.0050,0.0067,0.9829,0.0025</t>
-  </si>
-  <si>
-    <t>0.0116,0.0821,0.9572,0.0013</t>
-  </si>
-  <si>
-    <t>0.0706,0.0011,0.9200,0.0002</t>
-  </si>
-  <si>
-    <t>0.0099,0.0291,0.9454,0.0020</t>
-  </si>
-  <si>
-    <t>0.9993,0.0004,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9980,0.0017,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9979,0.0013,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9939,0.0046,0.0013,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0020,0.9998,0.0022</t>
-  </si>
-  <si>
-    <t>0.0438,0.7303,0.1035,0.0008</t>
-  </si>
-  <si>
-    <t>0.9984,0.0002,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.0630,0.0000,0.9690,0.0000</t>
-  </si>
-  <si>
-    <t>0.0195,0.0032,0.9736,0.0006</t>
-  </si>
-  <si>
-    <t>0.0033,0.0261,0.9845,0.0012</t>
-  </si>
-  <si>
-    <t>0.0007,0.0000,0.9991,0.0000</t>
-  </si>
-  <si>
-    <t>0.0083,0.0007,0.9878,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0013,0.0070,0.9951,0.0009</t>
-  </si>
-  <si>
-    <t>0.7186,0.0008,0.1818,0.0021</t>
-  </si>
-  <si>
-    <t>0.9485,0.0002,0.0332,0.0004</t>
-  </si>
-  <si>
-    <t>0.9952,0.0001,0.0021,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0005,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9997,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9964,0.0038,0.0004,0.0001</t>
+    <t>0.9981,0.0010,0.0005,0.0001</t>
   </si>
   <si>
     <t>0.9995,0.0002,0.0001,0.0001</t>
   </si>
   <si>
-    <t>0.9989,0.0014,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0004,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0006,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0004,0.9993,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0017,0.9989,0.0001</t>
-  </si>
-  <si>
-    <t>0.0008,0.0007,0.9975,0.0005</t>
-  </si>
-  <si>
-    <t>0.0091,0.0000,0.9911,0.0001</t>
-  </si>
-  <si>
-    <t>0.0046,0.0130,0.9456,0.0473</t>
-  </si>
-  <si>
-    <t>0.1232,0.0002,0.8772,0.0005</t>
-  </si>
-  <si>
-    <t>0.0112,0.0197,0.9358,0.0074</t>
-  </si>
-  <si>
-    <t>0.9911,0.0000,0.0024,0.0015</t>
-  </si>
-  <si>
-    <t>0.0000,0.0348,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0058,0.0000,0.0012,0.9953</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.9691,0.0002,0.0002,0.0182</t>
+    <t>0.9994,0.0006,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0006,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0020,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0099,0.9980,0.0003</t>
+  </si>
+  <si>
+    <t>0.0127,0.0168,0.9623,0.0008</t>
+  </si>
+  <si>
+    <t>0.0928,0.0003,0.9276,0.0002</t>
+  </si>
+  <si>
+    <t>0.0094,0.0040,0.9594,0.0200</t>
+  </si>
+  <si>
+    <t>0.0425,0.0003,0.9578,0.0002</t>
+  </si>
+  <si>
+    <t>0.0071,0.0011,0.9803,0.0068</t>
+  </si>
+  <si>
+    <t>0.9541,0.0000,0.0008,0.0269</t>
+  </si>
+  <si>
+    <t>0.0005,0.0023,0.0000,0.9995</t>
+  </si>
+  <si>
+    <t>0.0009,0.0000,0.0004,0.9992</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.9965,0.0001,0.0002,0.0008</t>
   </si>
 </sst>
 </file>
@@ -1872,7 +1857,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1886,7 +1871,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1900,7 +1885,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1914,7 +1899,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1928,7 +1913,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1970,7 +1955,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2012,7 +1997,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2026,7 +2011,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2037,7 +2022,7 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D14" t="s">
         <v>273</v>
@@ -2247,7 +2232,7 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D29" t="s">
         <v>288</v>
@@ -2460,7 +2445,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>281</v>
+        <v>303</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2474,7 +2459,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2488,7 +2473,7 @@
         <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2502,7 +2487,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2516,7 +2501,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2530,7 +2515,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2544,7 +2529,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2558,7 +2543,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2572,7 +2557,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2586,7 +2571,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2600,7 +2585,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2614,7 +2599,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2628,7 +2613,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2642,7 +2627,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2656,7 +2641,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>316</v>
+        <v>269</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2684,7 +2669,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>318</v>
+        <v>269</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2698,7 +2683,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2712,7 +2697,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2726,7 +2711,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2740,7 +2725,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2754,7 +2739,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2768,7 +2753,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2782,7 +2767,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2796,7 +2781,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2810,7 +2795,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2821,10 +2806,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2838,7 +2823,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2852,7 +2837,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2863,10 +2848,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2877,10 +2862,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D74" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2894,7 +2879,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2905,10 +2890,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2922,7 +2907,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2936,7 +2921,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2950,7 +2935,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2964,7 +2949,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2978,7 +2963,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2992,7 +2977,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3006,7 +2991,7 @@
         <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3020,7 +3005,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3034,7 +3019,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3045,10 +3030,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3062,7 +3047,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3076,7 +3061,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3090,7 +3075,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3104,7 +3089,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>268</v>
+        <v>346</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3160,7 +3145,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3174,7 +3159,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3188,7 +3173,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3202,7 +3187,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3216,7 +3201,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3230,7 +3215,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3244,7 +3229,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3258,7 +3243,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>353</v>
+        <v>271</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3272,7 +3257,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>269</v>
+        <v>349</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3286,7 +3271,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3300,7 +3285,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3314,7 +3299,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3328,7 +3313,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3339,10 +3324,10 @@
         <v>259</v>
       </c>
       <c r="C107" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D107" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3356,7 +3341,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3370,7 +3355,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3384,7 +3369,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3398,7 +3383,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3412,7 +3397,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3426,7 +3411,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3440,7 +3425,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>305</v>
+        <v>282</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3451,10 +3436,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3465,10 +3450,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D116" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3482,7 +3467,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3496,7 +3481,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3510,7 +3495,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3524,7 +3509,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3538,7 +3523,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3552,7 +3537,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3566,7 +3551,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>372</v>
+        <v>282</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3580,7 +3565,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>373</v>
+        <v>368</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3594,7 +3579,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3608,7 +3593,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>375</v>
+        <v>370</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3622,7 +3607,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3636,7 +3621,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3650,7 +3635,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>378</v>
+        <v>373</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3664,7 +3649,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>379</v>
+        <v>374</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3692,7 +3677,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>380</v>
+        <v>375</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3706,7 +3691,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>269</v>
+        <v>376</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3720,7 +3705,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3734,7 +3719,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3745,10 +3730,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3759,10 +3744,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3776,7 +3761,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3790,7 +3775,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>386</v>
+        <v>381</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3804,7 +3789,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3818,7 +3803,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>388</v>
+        <v>383</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3832,7 +3817,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3843,10 +3828,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D143" t="s">
-        <v>390</v>
+        <v>385</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3860,7 +3845,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>391</v>
+        <v>386</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3874,7 +3859,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>336</v>
+        <v>387</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3888,7 +3873,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>336</v>
+        <v>387</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3902,7 +3887,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3916,7 +3901,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3930,7 +3915,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>394</v>
+        <v>319</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3944,7 +3929,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3958,7 +3943,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3972,7 +3957,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3986,7 +3971,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4000,7 +3985,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4014,7 +3999,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4028,7 +4013,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4042,7 +4027,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4056,7 +4041,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>402</v>
+        <v>269</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4067,10 +4052,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4084,7 +4069,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4098,7 +4083,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4109,10 +4094,10 @@
         <v>262</v>
       </c>
       <c r="C162" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D162" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4126,7 +4111,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4140,7 +4125,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4154,7 +4139,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4168,7 +4153,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>269</v>
+        <v>346</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4182,7 +4167,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>269</v>
+        <v>404</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4196,7 +4181,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4224,7 +4209,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4238,7 +4223,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4252,7 +4237,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4266,7 +4251,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4277,10 +4262,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D174" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4294,7 +4279,7 @@
         <v>259</v>
       </c>
       <c r="D175" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4308,7 +4293,7 @@
         <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4322,7 +4307,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>418</v>
+        <v>346</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4336,7 +4321,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>419</v>
+        <v>413</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4364,7 +4349,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>420</v>
+        <v>414</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4378,7 +4363,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>421</v>
+        <v>415</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4392,7 +4377,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>422</v>
+        <v>416</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4406,7 +4391,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>423</v>
+        <v>417</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4420,7 +4405,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>424</v>
+        <v>418</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4434,7 +4419,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>425</v>
+        <v>419</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4448,7 +4433,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4462,7 +4447,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4476,7 +4461,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>428</v>
+        <v>422</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4490,7 +4475,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>429</v>
+        <v>423</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4504,7 +4489,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>430</v>
+        <v>424</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4518,7 +4503,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4532,7 +4517,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>432</v>
+        <v>426</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4546,7 +4531,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>433</v>
+        <v>427</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4560,7 +4545,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>434</v>
+        <v>428</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4571,10 +4556,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>435</v>
+        <v>429</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4585,10 +4570,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>436</v>
+        <v>430</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4602,7 +4587,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>437</v>
+        <v>431</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4616,7 +4601,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4630,7 +4615,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4644,7 +4629,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4655,10 +4640,10 @@
         <v>259</v>
       </c>
       <c r="C201" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D201" t="s">
-        <v>441</v>
+        <v>435</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4672,7 +4657,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>442</v>
+        <v>436</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4686,7 +4671,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>443</v>
+        <v>437</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4700,7 +4685,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>444</v>
+        <v>438</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4714,7 +4699,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>445</v>
+        <v>439</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4725,10 +4710,10 @@
         <v>261</v>
       </c>
       <c r="C206" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D206" t="s">
-        <v>446</v>
+        <v>440</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4742,7 +4727,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>447</v>
+        <v>441</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4756,7 +4741,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>448</v>
+        <v>442</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4770,7 +4755,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>449</v>
+        <v>443</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4784,7 +4769,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4798,7 +4783,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4812,7 +4797,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4826,7 +4811,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4840,7 +4825,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4854,7 +4839,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4868,7 +4853,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4882,7 +4867,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4896,7 +4881,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>349</v>
+        <v>452</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4910,7 +4895,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>453</v>
+        <v>269</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4924,7 +4909,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4938,7 +4923,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4949,10 +4934,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D222" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4966,7 +4951,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4980,7 +4965,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4994,7 +4979,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5008,7 +4993,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5022,7 +5007,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5036,7 +5021,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5050,7 +5035,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5064,7 +5049,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5078,7 +5063,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5092,7 +5077,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5106,7 +5091,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5120,7 +5105,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5134,7 +5119,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5148,7 +5133,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>320</v>
+        <v>346</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5162,7 +5147,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5176,7 +5161,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5190,7 +5175,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5204,7 +5189,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>319</v>
+        <v>346</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5218,7 +5203,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5232,7 +5217,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>477</v>
+        <v>349</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5246,7 +5231,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5260,7 +5245,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5274,7 +5259,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5288,7 +5273,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5302,7 +5287,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5316,7 +5301,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5330,7 +5315,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5344,7 +5329,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5358,7 +5343,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5372,7 +5357,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5386,7 +5371,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5400,7 +5385,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>336</v>
+        <v>483</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5414,7 +5399,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5428,7 +5413,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
     </row>
   </sheetData>
